--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Jefferson</t>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -656,9 +659,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,13 +753,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>43.64283</v>
@@ -803,12 +810,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>44.14558</v>
@@ -856,12 +863,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>44.14166</v>
@@ -909,12 +916,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>43.79211</v>
@@ -962,12 +969,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>44.09325</v>
@@ -1018,12 +1025,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>43.33278</v>
@@ -1071,12 +1078,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>43.60234</v>
@@ -1127,12 +1134,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>42.6994</v>
@@ -1183,12 +1190,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>42.64497</v>
@@ -1239,12 +1246,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>42.64432</v>
@@ -1295,12 +1302,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>42.69457</v>
@@ -1348,12 +1355,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>42.54479</v>
@@ -1404,12 +1411,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>42.54348</v>
@@ -1457,12 +1464,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15">
         <v>42.58318</v>
@@ -1513,12 +1520,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>43.44244</v>
@@ -1568,10 +1575,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>43.43774</v>
@@ -1621,10 +1628,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>43.43142</v>
@@ -1674,10 +1681,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19">
         <v>43.43121</v>
@@ -1727,10 +1734,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>43.64283</v>
@@ -1780,10 +1787,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <v>42.10207</v>
@@ -1833,10 +1840,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>42.11042</v>
@@ -1886,10 +1893,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>42.08359</v>
@@ -1939,10 +1946,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24">
         <v>42.09787</v>
@@ -1992,10 +1999,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <v>42.72589</v>
@@ -2045,10 +2052,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26">
         <v>42.23667</v>
@@ -2098,10 +2105,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>42.107989</v>
@@ -2151,10 +2158,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>42.10776</v>
@@ -2204,10 +2211,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>42.09656</v>
@@ -2257,10 +2264,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>43.36414</v>
@@ -2310,10 +2317,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31">
         <v>43.42818</v>
@@ -2363,10 +2370,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32">
         <v>43.42341</v>
@@ -2416,10 +2423,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33">
         <v>43.42322</v>
@@ -2469,10 +2476,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>43.29241</v>
@@ -2522,10 +2529,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C35">
         <v>43.3829</v>
@@ -2575,10 +2582,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>43.32777</v>
@@ -2628,10 +2635,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>43.12966</v>
@@ -2681,10 +2688,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>42.17334</v>
@@ -2734,10 +2741,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>42.08533</v>
@@ -2787,10 +2794,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>42.47663</v>
@@ -2840,10 +2847,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>42.70399</v>
@@ -2893,10 +2900,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>42.68841</v>
@@ -2946,10 +2953,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43">
         <v>42.68841</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/before_conversion_caes2014_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
   <si>
     <t>location</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Banbury Hot Springs</t>
+  </si>
+  <si>
+    <t>Basalt</t>
   </si>
 </sst>
 </file>
@@ -770,6 +773,9 @@
       <c r="D2">
         <v>-111.68768</v>
       </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
       <c r="H2">
         <v>48.2</v>
       </c>
@@ -823,6 +829,9 @@
       <c r="D3">
         <v>-112.55494</v>
       </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
       <c r="H3">
         <v>56.1</v>
       </c>
@@ -876,6 +885,9 @@
       <c r="D4">
         <v>-112.5524</v>
       </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
       <c r="H4">
         <v>52.3</v>
       </c>
@@ -929,6 +941,9 @@
       <c r="D5">
         <v>-111.44009</v>
       </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
       <c r="H5">
         <v>44</v>
       </c>
@@ -985,6 +1000,9 @@
       <c r="E6">
         <v>1216.7616</v>
       </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
       <c r="H6">
         <v>31.4</v>
       </c>
@@ -1038,6 +1056,9 @@
       <c r="D7">
         <v>-113.9179</v>
       </c>
+      <c r="F7" t="s">
+        <v>84</v>
+      </c>
       <c r="H7">
         <v>50.5</v>
       </c>
@@ -1094,6 +1115,9 @@
       <c r="E8">
         <v>272.1864</v>
       </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
       <c r="H8">
         <v>36.3</v>
       </c>
@@ -1150,6 +1174,9 @@
       <c r="E9">
         <v>243.84</v>
       </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
       <c r="H9">
         <v>24.7</v>
       </c>
@@ -1206,6 +1233,9 @@
       <c r="E10">
         <v>327.66</v>
       </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
       <c r="H10">
         <v>34.5</v>
       </c>
@@ -1262,6 +1292,9 @@
       <c r="E11">
         <v>320.04</v>
       </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
       <c r="H11">
         <v>34.4</v>
       </c>
@@ -1315,6 +1348,9 @@
       <c r="D12">
         <v>-114.85592</v>
       </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
       <c r="H12">
         <v>58.4</v>
       </c>
@@ -1371,6 +1407,9 @@
       <c r="E13">
         <v>445.008</v>
       </c>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
       <c r="H13">
         <v>37.5</v>
       </c>
@@ -1424,6 +1463,9 @@
       <c r="D14">
         <v>-114.94897</v>
       </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
       <c r="H14">
         <v>36.2</v>
       </c>
@@ -1480,6 +1522,9 @@
       <c r="E15">
         <v>451.104</v>
       </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
       <c r="H15">
         <v>38.1</v>
       </c>
@@ -1533,6 +1578,9 @@
       <c r="D16">
         <v>-111.90484</v>
       </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
       <c r="H16">
         <v>20.9</v>
       </c>
@@ -1586,6 +1634,9 @@
       <c r="D17">
         <v>-111.93018</v>
       </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
       <c r="H17">
         <v>27.7</v>
       </c>
@@ -1639,6 +1690,9 @@
       <c r="D18">
         <v>-111.94501</v>
       </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
       <c r="H18">
         <v>26.8</v>
       </c>
@@ -1692,6 +1746,9 @@
       <c r="D19">
         <v>-111.94469</v>
       </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
       <c r="H19">
         <v>25.1</v>
       </c>
@@ -1745,6 +1802,9 @@
       <c r="D20">
         <v>-111.68768</v>
       </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
       <c r="H20">
         <v>48.6</v>
       </c>
@@ -1798,6 +1858,9 @@
       <c r="D21">
         <v>-113.38434</v>
       </c>
+      <c r="F21" t="s">
+        <v>84</v>
+      </c>
       <c r="H21">
         <v>59.7</v>
       </c>
@@ -1851,6 +1914,9 @@
       <c r="D22">
         <v>-113.37519</v>
       </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
       <c r="H22">
         <v>47.9</v>
       </c>
@@ -1904,6 +1970,9 @@
       <c r="D23">
         <v>-113.35865</v>
       </c>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
       <c r="H23">
         <v>48</v>
       </c>
@@ -1957,6 +2026,9 @@
       <c r="D24">
         <v>-113.38541</v>
       </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
       <c r="H24">
         <v>48.3</v>
       </c>
@@ -2010,6 +2082,9 @@
       <c r="D25">
         <v>-112.87381</v>
       </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
       <c r="H25">
         <v>32.7</v>
       </c>
@@ -2063,6 +2138,9 @@
       <c r="D26">
         <v>-113.36971</v>
       </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
       <c r="H26">
         <v>54.7</v>
       </c>
@@ -2116,6 +2194,9 @@
       <c r="D27">
         <v>-113.39206</v>
       </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
       <c r="H27">
         <v>44.7</v>
       </c>
@@ -2169,6 +2250,9 @@
       <c r="D28">
         <v>-113.39186</v>
       </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
       <c r="H28">
         <v>40.9</v>
       </c>
@@ -2222,6 +2306,9 @@
       <c r="D29">
         <v>-113.378</v>
       </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
       <c r="H29">
         <v>26</v>
       </c>
@@ -2275,6 +2362,9 @@
       <c r="D30">
         <v>-113.78943</v>
       </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
       <c r="H30">
         <v>38.1</v>
       </c>
@@ -2328,6 +2418,9 @@
       <c r="D31">
         <v>-114.39941</v>
       </c>
+      <c r="F31" t="s">
+        <v>84</v>
+      </c>
       <c r="H31">
         <v>39.1</v>
       </c>
@@ -2381,6 +2474,9 @@
       <c r="D32">
         <v>-114.62857</v>
       </c>
+      <c r="F32" t="s">
+        <v>84</v>
+      </c>
       <c r="H32">
         <v>50</v>
       </c>
@@ -2434,6 +2530,9 @@
       <c r="D33">
         <v>-114.62865</v>
       </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
       <c r="H33">
         <v>55.5</v>
       </c>
@@ -2487,6 +2586,9 @@
       <c r="D34">
         <v>-114.91002</v>
       </c>
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
       <c r="H34">
         <v>38</v>
       </c>
@@ -2540,6 +2642,9 @@
       <c r="D35">
         <v>-114.93224</v>
       </c>
+      <c r="F35" t="s">
+        <v>84</v>
+      </c>
       <c r="H35">
         <v>67.5</v>
       </c>
@@ -2593,6 +2698,9 @@
       <c r="D36">
         <v>-114.39941</v>
       </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
       <c r="H36">
         <v>75</v>
       </c>
@@ -2646,6 +2754,9 @@
       <c r="D37">
         <v>-115.33841</v>
       </c>
+      <c r="F37" t="s">
+        <v>84</v>
+      </c>
       <c r="H37">
         <v>57.7</v>
       </c>
@@ -2699,6 +2810,9 @@
       <c r="D38">
         <v>-113.86163</v>
       </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
       <c r="H38">
         <v>46.9</v>
       </c>
@@ -2752,6 +2866,9 @@
       <c r="D39">
         <v>-113.93984</v>
       </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
       <c r="H39">
         <v>45.7</v>
       </c>
@@ -2805,6 +2922,9 @@
       <c r="D40">
         <v>-113.5077</v>
       </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
       <c r="H40">
         <v>59.6</v>
       </c>
@@ -2858,6 +2978,9 @@
       <c r="D41">
         <v>-114.85699</v>
       </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
       <c r="H41">
         <v>72</v>
       </c>
@@ -2911,6 +3034,9 @@
       <c r="D42">
         <v>-114.8268</v>
       </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
       <c r="H42">
         <v>58.8</v>
       </c>
@@ -2963,6 +3089,9 @@
       </c>
       <c r="D43">
         <v>-114.8268</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
       </c>
       <c r="H43">
         <v>58.5</v>
